--- a/consent_forms/030_wags_to_whiskers_new_client_info_form--consent_forms.xlsx
+++ b/consent_forms/030_wags_to_whiskers_new_client_info_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'individual',_'value':_'individual'}</t>
+          <t>individual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Individual', 'value': 'individual'}</t>
+          <t>Individual</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'business',_'value':_'business'}</t>
+          <t>business</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Business', 'value': 'business'}</t>
+          <t>Business</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'1-10',_'value':_'1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '1-10', 'value': '1-10'}</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'11-50',_'value':_'11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '11-50', 'value': '11-50'}</t>
+          <t>11-50</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'51-100',_'value':_'51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '51-100', 'value': '51-100'}</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'101-200',_'value':_'101-200'}</t>
+          <t>101-200</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '101-200', 'value': '101-200'}</t>
+          <t>101-200</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'200+',_'value':_'200+'}</t>
+          <t>200+</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '200+', 'value': '200+'}</t>
+          <t>200+</t>
         </is>
       </c>
     </row>
